--- a/fhir/StructureDefinition-ehealth-usage.xlsx
+++ b/fhir/StructureDefinition-ehealth-usage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-usage.xlsx
+++ b/fhir/StructureDefinition-ehealth-usage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-usage.xlsx
+++ b/fhir/StructureDefinition-ehealth-usage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-usage.xlsx
+++ b/fhir/StructureDefinition-ehealth-usage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-usage.xlsx
+++ b/fhir/StructureDefinition-ehealth-usage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-usage.xlsx
+++ b/fhir/StructureDefinition-ehealth-usage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-usage.xlsx
+++ b/fhir/StructureDefinition-ehealth-usage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
